--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/56.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/56.xlsx
@@ -426,13 +426,13 @@
         <v>-3.846213749476068</v>
       </c>
       <c r="E2">
-        <v>-3.785371613615284</v>
+        <v>-3.268505175801813</v>
       </c>
       <c r="F2">
-        <v>-6.612539016853792</v>
+        <v>-6.709862100548813</v>
       </c>
       <c r="G2">
-        <v>-0.7679384677764534</v>
+        <v>-1.129850616675119</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.024022261349326</v>
       </c>
       <c r="E3">
-        <v>-3.496151564167402</v>
+        <v>-3.713572658223671</v>
       </c>
       <c r="F3">
-        <v>-6.900290067233083</v>
+        <v>-6.460462468544282</v>
       </c>
       <c r="G3">
-        <v>-0.6120680521509481</v>
+        <v>-0.7951114255627912</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.283413735926801</v>
       </c>
       <c r="E4">
-        <v>-3.846247889700397</v>
+        <v>-4.352997716580733</v>
       </c>
       <c r="F4">
-        <v>-7.092015880915056</v>
+        <v>-6.757829385315643</v>
       </c>
       <c r="G4">
-        <v>-0.8528473397676808</v>
+        <v>-0.1242227509384067</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.737277620830951</v>
       </c>
       <c r="E5">
-        <v>-4.603426857678912</v>
+        <v>-4.655114860002461</v>
       </c>
       <c r="F5">
-        <v>-7.057328762102144</v>
+        <v>-6.658931306087718</v>
       </c>
       <c r="G5">
-        <v>-0.4916602003421157</v>
+        <v>-0.9831305489201591</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.352316113259572</v>
       </c>
       <c r="E6">
-        <v>-5.281285074939072</v>
+        <v>-5.369771457048951</v>
       </c>
       <c r="F6">
-        <v>-6.747922117035134</v>
+        <v>-6.94884530282102</v>
       </c>
       <c r="G6">
-        <v>-0.2690491866449033</v>
+        <v>-1.225793536948737</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.127890123504131</v>
       </c>
       <c r="E7">
-        <v>-6.931094196939529</v>
+        <v>-6.160284522197927</v>
       </c>
       <c r="F7">
-        <v>-6.840286617508914</v>
+        <v>-6.644238474457228</v>
       </c>
       <c r="G7">
-        <v>-0.804410747982604</v>
+        <v>-1.056505480252566</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.028908478356909</v>
       </c>
       <c r="E8">
-        <v>-7.141283318005549</v>
+        <v>-7.078523196733245</v>
       </c>
       <c r="F8">
-        <v>-6.934019835820113</v>
+        <v>-6.519324858156378</v>
       </c>
       <c r="G8">
-        <v>0.4295686174164168</v>
+        <v>-1.278080293195986</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.026146680730018</v>
       </c>
       <c r="E9">
-        <v>-8.533345284911432</v>
+        <v>-7.551739673586782</v>
       </c>
       <c r="F9">
-        <v>-6.948869454336231</v>
+        <v>-6.609929861358106</v>
       </c>
       <c r="G9">
-        <v>-1.024813627805123</v>
+        <v>-1.694881287135768</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.076274249650615</v>
       </c>
       <c r="E10">
-        <v>-9.216325206274268</v>
+        <v>-8.25337690786122</v>
       </c>
       <c r="F10">
-        <v>-7.0163531430255</v>
+        <v>-6.554318028137449</v>
       </c>
       <c r="G10">
-        <v>-1.196581283110208</v>
+        <v>-1.537521126017591</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.138434563803771</v>
       </c>
       <c r="E11">
-        <v>-9.55285875215429</v>
+        <v>-9.450085034550211</v>
       </c>
       <c r="F11">
-        <v>-6.452421993611597</v>
+        <v>-6.504988360356863</v>
       </c>
       <c r="G11">
-        <v>-0.73175089448668</v>
+        <v>-1.965948755891293</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.173858604801264</v>
       </c>
       <c r="E12">
-        <v>-9.956282387601611</v>
+        <v>-9.778381286210282</v>
       </c>
       <c r="F12">
-        <v>-6.73415416965926</v>
+        <v>-6.250719228588834</v>
       </c>
       <c r="G12">
-        <v>-0.632417975580848</v>
+        <v>-1.463464222304094</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.146120656830546</v>
       </c>
       <c r="E13">
-        <v>-10.96883106182067</v>
+        <v>-11.09084626548334</v>
       </c>
       <c r="F13">
-        <v>-6.386172803683412</v>
+        <v>-6.233628666202369</v>
       </c>
       <c r="G13">
-        <v>-0.9482804360282513</v>
+        <v>-1.801364984406426</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.03373115201115</v>
       </c>
       <c r="E14">
-        <v>-11.10018850736117</v>
+        <v>-12.70919607855251</v>
       </c>
       <c r="F14">
-        <v>-6.139553367413435</v>
+        <v>-5.872741680721605</v>
       </c>
       <c r="G14">
-        <v>0.05200089866253789</v>
+        <v>-1.752517884974479</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.8241570727859454</v>
       </c>
       <c r="E15">
-        <v>-12.30926842503911</v>
+        <v>-11.70699496744098</v>
       </c>
       <c r="F15">
-        <v>-6.297412421946693</v>
+        <v>-5.55282833468509</v>
       </c>
       <c r="G15">
-        <v>-0.01137949568680898</v>
+        <v>-1.559513080034969</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.5224228614706679</v>
       </c>
       <c r="E16">
-        <v>-12.74253470419698</v>
+        <v>-12.21641206551183</v>
       </c>
       <c r="F16">
-        <v>-5.638615308565572</v>
+        <v>-5.475428667332776</v>
       </c>
       <c r="G16">
-        <v>0.1388729241585531</v>
+        <v>-0.3223853858281014</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.1469601011840526</v>
       </c>
       <c r="E17">
-        <v>-13.65710078631208</v>
+        <v>-14.24716094951153</v>
       </c>
       <c r="F17">
-        <v>-5.553825277558859</v>
+        <v>-5.421901782949796</v>
       </c>
       <c r="G17">
-        <v>0.4486870179057079</v>
+        <v>0.6558146101157489</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.2700482184501113</v>
       </c>
       <c r="E18">
-        <v>-13.74329576057408</v>
+        <v>-13.20174461094479</v>
       </c>
       <c r="F18">
-        <v>-5.436317466045083</v>
+        <v>-4.940276225887759</v>
       </c>
       <c r="G18">
-        <v>0.2293501337468347</v>
+        <v>0.1065421364220307</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.6858427924970485</v>
       </c>
       <c r="E19">
-        <v>-15.81188910185587</v>
+        <v>-16.0106302406305</v>
       </c>
       <c r="F19">
-        <v>-5.001427070547665</v>
+        <v>-4.754060916938558</v>
       </c>
       <c r="G19">
-        <v>0.5544126002478725</v>
+        <v>0.8535336319031813</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.055329285690909</v>
       </c>
       <c r="E20">
-        <v>-16.24408213267393</v>
+        <v>-16.40272816258464</v>
       </c>
       <c r="F20">
-        <v>-5.06856828283272</v>
+        <v>-4.313309225848098</v>
       </c>
       <c r="G20">
-        <v>1.02142794892732</v>
+        <v>0.5344731844648422</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.337448913751245</v>
       </c>
       <c r="E21">
-        <v>-16.7171446414112</v>
+        <v>-17.5072003306854</v>
       </c>
       <c r="F21">
-        <v>-4.518380929279479</v>
+        <v>-4.524557382349693</v>
       </c>
       <c r="G21">
-        <v>1.195254763557832</v>
+        <v>0.8278471090639762</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.500294289263501</v>
       </c>
       <c r="E22">
-        <v>-17.61485574326975</v>
+        <v>-18.00187271738728</v>
       </c>
       <c r="F22">
-        <v>-4.329788477751204</v>
+        <v>-4.014297630483553</v>
       </c>
       <c r="G22">
-        <v>1.227588861839894</v>
+        <v>1.31109406252247</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.524985061724271</v>
       </c>
       <c r="E23">
-        <v>-17.98743594225083</v>
+        <v>-19.58447022816589</v>
       </c>
       <c r="F23">
-        <v>-3.992003802311912</v>
+        <v>-3.788039109315423</v>
       </c>
       <c r="G23">
-        <v>0.9423621898129059</v>
+        <v>0.2970541005704697</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.405073604807706</v>
       </c>
       <c r="E24">
-        <v>-18.30005461689634</v>
+        <v>-18.88568593251629</v>
       </c>
       <c r="F24">
-        <v>-3.859114247094431</v>
+        <v>-3.946458795742747</v>
       </c>
       <c r="G24">
-        <v>0.2598137737992081</v>
+        <v>0.9392370348238338</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.147434952634682</v>
       </c>
       <c r="E25">
-        <v>-19.22311611624983</v>
+        <v>-19.38960546314183</v>
       </c>
       <c r="F25">
-        <v>-3.662684826843603</v>
+        <v>-3.100551579570201</v>
       </c>
       <c r="G25">
-        <v>0.1231809383024077</v>
+        <v>0.3771659920752932</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.7710901038701784</v>
       </c>
       <c r="E26">
-        <v>-18.55148907922423</v>
+        <v>-19.38618646526604</v>
       </c>
       <c r="F26">
-        <v>-3.703608579551516</v>
+        <v>-3.907205852775622</v>
       </c>
       <c r="G26">
-        <v>-0.0146403830429911</v>
+        <v>0.2618298960326242</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.3035929535594664</v>
       </c>
       <c r="E27">
-        <v>-18.33290869582199</v>
+        <v>-20.72693629319101</v>
       </c>
       <c r="F27">
-        <v>-3.498140949641275</v>
+        <v>-3.443899813890432</v>
       </c>
       <c r="G27">
-        <v>-0.1001418426857481</v>
+        <v>0.2880229323393379</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.21707402911451</v>
       </c>
       <c r="E28">
-        <v>-18.91499874476794</v>
+        <v>-20.26360094662221</v>
       </c>
       <c r="F28">
-        <v>-3.702801681387599</v>
+        <v>-3.380185741206387</v>
       </c>
       <c r="G28">
-        <v>-0.8778684429534924</v>
+        <v>-0.5923669956467452</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.7504195829463579</v>
       </c>
       <c r="E29">
-        <v>-19.35236329290275</v>
+        <v>-19.12722115066341</v>
       </c>
       <c r="F29">
-        <v>-3.50337588954476</v>
+        <v>-3.51925966802366</v>
       </c>
       <c r="G29">
-        <v>-0.596197296835682</v>
+        <v>-0.610932535030978</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.255047112371441</v>
       </c>
       <c r="E30">
-        <v>-19.29303575492826</v>
+        <v>-19.77242907032826</v>
       </c>
       <c r="F30">
-        <v>-3.433707082618663</v>
+        <v>-3.896762895969215</v>
       </c>
       <c r="G30">
-        <v>-1.323328829626745</v>
+        <v>-0.2191493337314687</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.69566570892873</v>
       </c>
       <c r="E31">
-        <v>-19.54858660012912</v>
+        <v>-19.86572469183429</v>
       </c>
       <c r="F31">
-        <v>-3.881021651022704</v>
+        <v>-3.578060293105053</v>
       </c>
       <c r="G31">
-        <v>-1.40179869054409</v>
+        <v>-0.4325603413750465</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.047187090322108</v>
       </c>
       <c r="E32">
-        <v>-18.31304680882435</v>
+        <v>-19.38847787311392</v>
       </c>
       <c r="F32">
-        <v>-3.610335427808752</v>
+        <v>-3.957499601532233</v>
       </c>
       <c r="G32">
-        <v>-1.355096824621591</v>
+        <v>-0.8302098293701444</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.291851930365797</v>
       </c>
       <c r="E33">
-        <v>-18.15604008650441</v>
+        <v>-19.13363346985827</v>
       </c>
       <c r="F33">
-        <v>-3.920832850325021</v>
+        <v>-3.961269613463937</v>
       </c>
       <c r="G33">
-        <v>-0.6418033721846819</v>
+        <v>-0.1824486258831083</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.42452986444739</v>
       </c>
       <c r="E34">
-        <v>-19.29317160914849</v>
+        <v>-18.3700512396329</v>
       </c>
       <c r="F34">
-        <v>-3.805234988145265</v>
+        <v>-3.573947408842657</v>
       </c>
       <c r="G34">
-        <v>-0.2946032876625376</v>
+        <v>-0.7985974300156439</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.447580778451806</v>
       </c>
       <c r="E35">
-        <v>-18.3885274135842</v>
+        <v>-17.75383008209115</v>
       </c>
       <c r="F35">
-        <v>-3.858750786586837</v>
+        <v>-3.929169478263894</v>
       </c>
       <c r="G35">
-        <v>-0.06121644823499743</v>
+        <v>0.1590010410373219</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.371850901942602</v>
       </c>
       <c r="E36">
-        <v>-17.44611574479594</v>
+        <v>-18.67969470685538</v>
       </c>
       <c r="F36">
-        <v>-3.708502230830224</v>
+        <v>-3.397756958338188</v>
       </c>
       <c r="G36">
-        <v>0.05769172644454507</v>
+        <v>-1.010455791801304</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.212426685821205</v>
       </c>
       <c r="E37">
-        <v>-18.08202670732305</v>
+        <v>-18.06134516653002</v>
       </c>
       <c r="F37">
-        <v>-4.025184024946284</v>
+        <v>-3.640005366281552</v>
       </c>
       <c r="G37">
-        <v>0.5168577716503802</v>
+        <v>-0.287161181290256</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.986272188533493</v>
       </c>
       <c r="E38">
-        <v>-16.3467381099538</v>
+        <v>-17.8767826798734</v>
       </c>
       <c r="F38">
-        <v>-3.708117390292772</v>
+        <v>-3.507088888063508</v>
       </c>
       <c r="G38">
-        <v>0.8702518868765008</v>
+        <v>-0.5658263520584081</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.709984210902158</v>
       </c>
       <c r="E39">
-        <v>-16.73583365364086</v>
+        <v>-17.49244203389441</v>
       </c>
       <c r="F39">
-        <v>-4.056726695664092</v>
+        <v>-3.746934022280193</v>
       </c>
       <c r="G39">
-        <v>0.1292458577303525</v>
+        <v>0.9128817817856959</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.40155202682088</v>
       </c>
       <c r="E40">
-        <v>-16.21165825877901</v>
+        <v>-16.89393173819665</v>
       </c>
       <c r="F40">
-        <v>-3.763617572246389</v>
+        <v>-3.092951374882008</v>
       </c>
       <c r="G40">
-        <v>0.7156659629202328</v>
+        <v>0.1271271085852189</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.077832271515718</v>
       </c>
       <c r="E41">
-        <v>-16.2955482397711</v>
+        <v>-16.75603064771507</v>
       </c>
       <c r="F41">
-        <v>-3.975671043205985</v>
+        <v>-3.847274461670605</v>
       </c>
       <c r="G41">
-        <v>0.6772834979379226</v>
+        <v>0.2221861131998518</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.7554102221245754</v>
       </c>
       <c r="E42">
-        <v>-16.48755100922232</v>
+        <v>-16.4201809014102</v>
       </c>
       <c r="F42">
-        <v>-3.868379718552709</v>
+        <v>-4.022566159068063</v>
       </c>
       <c r="G42">
-        <v>0.2252582994602955</v>
+        <v>0.3073201022877496</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.4456577713662654</v>
       </c>
       <c r="E43">
-        <v>-15.94939621509879</v>
+        <v>-15.1328444244057</v>
       </c>
       <c r="F43">
-        <v>-3.800379345808528</v>
+        <v>-3.442519614185126</v>
       </c>
       <c r="G43">
-        <v>0.5593088971004546</v>
+        <v>0.8374708649466376</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.1557726083156178</v>
       </c>
       <c r="E44">
-        <v>-14.87292813026146</v>
+        <v>-13.78477205401033</v>
       </c>
       <c r="F44">
-        <v>-3.8244611779587</v>
+        <v>-3.661173179547315</v>
       </c>
       <c r="G44">
-        <v>1.600293389196583</v>
+        <v>0.4871853519818925</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.1085217708510272</v>
       </c>
       <c r="E45">
-        <v>-14.90114958027726</v>
+        <v>-13.59920424612402</v>
       </c>
       <c r="F45">
-        <v>-3.877653108540565</v>
+        <v>-3.908193293413899</v>
       </c>
       <c r="G45">
-        <v>1.763731711924862</v>
+        <v>0.3428223926508939</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.3459507767142876</v>
       </c>
       <c r="E46">
-        <v>-15.05528525007633</v>
+        <v>-13.75426372462066</v>
       </c>
       <c r="F46">
-        <v>-3.727426724666767</v>
+        <v>-3.577638235478589</v>
       </c>
       <c r="G46">
-        <v>0.5727894385363669</v>
+        <v>1.125647233049116</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.5522132970951523</v>
       </c>
       <c r="E47">
-        <v>-14.39634246874621</v>
+        <v>-13.77345539746516</v>
       </c>
       <c r="F47">
-        <v>-4.099015602871114</v>
+        <v>-4.171942092865269</v>
       </c>
       <c r="G47">
-        <v>1.668358205483999</v>
+        <v>1.495345785056147</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.7270104138460303</v>
       </c>
       <c r="E48">
-        <v>-13.89001378994859</v>
+        <v>-13.85795219397428</v>
       </c>
       <c r="F48">
-        <v>-4.150879596042882</v>
+        <v>-3.766366093862635</v>
       </c>
       <c r="G48">
-        <v>1.27221170516373</v>
+        <v>0.8806503104153517</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.867364852301555</v>
       </c>
       <c r="E49">
-        <v>-13.72679852976414</v>
+        <v>-13.26465417185935</v>
       </c>
       <c r="F49">
-        <v>-4.176992531029605</v>
+        <v>-4.080125158711752</v>
       </c>
       <c r="G49">
-        <v>1.29119768383145</v>
+        <v>0.1836050154851854</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.9696517103294078</v>
       </c>
       <c r="E50">
-        <v>-13.8463909998327</v>
+        <v>-11.71352049848603</v>
       </c>
       <c r="F50">
-        <v>-4.202889290158871</v>
+        <v>-4.060287658414957</v>
       </c>
       <c r="G50">
-        <v>1.067378321012404</v>
+        <v>0.9118886181239145</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.030715925589702</v>
       </c>
       <c r="E51">
-        <v>-12.38344935775876</v>
+        <v>-12.55637819468967</v>
       </c>
       <c r="F51">
-        <v>-4.136209728148167</v>
+        <v>-4.062987085147824</v>
       </c>
       <c r="G51">
-        <v>0.8259865824709058</v>
+        <v>0.8406225043000237</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.048051031645343</v>
       </c>
       <c r="E52">
-        <v>-13.05912937902123</v>
+        <v>-11.23754165248782</v>
       </c>
       <c r="F52">
-        <v>-4.12789131282732</v>
+        <v>-3.591398264324885</v>
       </c>
       <c r="G52">
-        <v>1.43837129632529</v>
+        <v>0.4828518478709865</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.021149834034658</v>
       </c>
       <c r="E53">
-        <v>-13.67261986673637</v>
+        <v>-12.17137639150555</v>
       </c>
       <c r="F53">
-        <v>-4.419849082044498</v>
+        <v>-4.013546953879635</v>
       </c>
       <c r="G53">
-        <v>1.615604662315712</v>
+        <v>1.051411559876499</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.9512149837481889</v>
       </c>
       <c r="E54">
-        <v>-11.83696217146112</v>
+        <v>-11.86985247817883</v>
       </c>
       <c r="F54">
-        <v>-4.198869844545486</v>
+        <v>-4.145068187186177</v>
       </c>
       <c r="G54">
-        <v>1.688602191456642</v>
+        <v>0.7319770207922219</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.8366404290155025</v>
       </c>
       <c r="E55">
-        <v>-12.45122249975756</v>
+        <v>-10.54043742069506</v>
       </c>
       <c r="F55">
-        <v>-4.753945306406731</v>
+        <v>-4.298330535299872</v>
       </c>
       <c r="G55">
-        <v>1.527650088428355</v>
+        <v>1.344037301183757</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.6761962547397423</v>
       </c>
       <c r="E56">
-        <v>-11.25521175806575</v>
+        <v>-10.47695727205553</v>
       </c>
       <c r="F56">
-        <v>-4.337923975038816</v>
+        <v>-4.24749911838497</v>
       </c>
       <c r="G56">
-        <v>1.155077982893237</v>
+        <v>1.416220436122027</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.4665685303204486</v>
       </c>
       <c r="E57">
-        <v>-11.50967124103075</v>
+        <v>-9.729138659850873</v>
       </c>
       <c r="F57">
-        <v>-4.513225174671766</v>
+        <v>-4.492019352464032</v>
       </c>
       <c r="G57">
-        <v>0.902529705884395</v>
+        <v>1.020974404188439</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.2061911523960085</v>
       </c>
       <c r="E58">
-        <v>-12.03263300485855</v>
+        <v>-10.56317488868757</v>
       </c>
       <c r="F58">
-        <v>-4.782344320882391</v>
+        <v>-3.922848907955375</v>
       </c>
       <c r="G58">
-        <v>1.338078319213069</v>
+        <v>0.1823370765436445</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.1031505598724894</v>
       </c>
       <c r="E59">
-        <v>-11.54963955262245</v>
+        <v>-9.14729314850134</v>
       </c>
       <c r="F59">
-        <v>-4.294324551186768</v>
+        <v>-4.26215710848532</v>
       </c>
       <c r="G59">
-        <v>1.647336241309627</v>
+        <v>0.5842439261022452</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.4605917095246832</v>
       </c>
       <c r="E60">
-        <v>-11.06687252408674</v>
+        <v>-9.239040031896742</v>
       </c>
       <c r="F60">
-        <v>-4.317372223374158</v>
+        <v>-4.042667346399778</v>
       </c>
       <c r="G60">
-        <v>0.9194101775891387</v>
+        <v>0.1363535990031677</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.8578961767869623</v>
       </c>
       <c r="E61">
-        <v>-11.33213241756003</v>
+        <v>-10.32114606687362</v>
       </c>
       <c r="F61">
-        <v>-4.216041175933638</v>
+        <v>-4.371538133094018</v>
       </c>
       <c r="G61">
-        <v>1.525974952385484</v>
+        <v>0.6499450128746211</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.29142796274307</v>
       </c>
       <c r="E62">
-        <v>-11.62407860836053</v>
+        <v>-9.703978458264258</v>
       </c>
       <c r="F62">
-        <v>-4.218223522685114</v>
+        <v>-4.201895514696933</v>
       </c>
       <c r="G62">
-        <v>1.180880374826316</v>
+        <v>0.6630812575744492</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.749918796663241</v>
       </c>
       <c r="E63">
-        <v>-10.32043509645442</v>
+        <v>-8.354783026314982</v>
       </c>
       <c r="F63">
-        <v>-4.388745097865268</v>
+        <v>-4.340521252740136</v>
       </c>
       <c r="G63">
-        <v>1.329434484810032</v>
+        <v>-0.1169296191153922</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.222474250010044</v>
       </c>
       <c r="E64">
-        <v>-10.74278322477979</v>
+        <v>-10.17395707620231</v>
       </c>
       <c r="F64">
-        <v>-4.4736602416393</v>
+        <v>-4.552671329760574</v>
       </c>
       <c r="G64">
-        <v>0.2991596075334462</v>
+        <v>-0.9085737528302327</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.695105994200431</v>
       </c>
       <c r="E65">
-        <v>-11.70377522242153</v>
+        <v>-9.170329495778359</v>
       </c>
       <c r="F65">
-        <v>-4.254975794011759</v>
+        <v>-4.241056602720962</v>
       </c>
       <c r="G65">
-        <v>0.4605520131184558</v>
+        <v>-1.054403283835128</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.151114801204434</v>
       </c>
       <c r="E66">
-        <v>-11.0419976163626</v>
+        <v>-9.231264642025572</v>
       </c>
       <c r="F66">
-        <v>-4.110386611343968</v>
+        <v>-3.993596218609886</v>
       </c>
       <c r="G66">
-        <v>0.3144311541061042</v>
+        <v>-0.8191890232699106</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.578360235465317</v>
       </c>
       <c r="E67">
-        <v>-10.12978634073149</v>
+        <v>-10.12041692800962</v>
       </c>
       <c r="F67">
-        <v>-4.42558526487022</v>
+        <v>-4.511382532839152</v>
       </c>
       <c r="G67">
-        <v>0.6932899856202988</v>
+        <v>-0.9212233473357878</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.959536182912236</v>
       </c>
       <c r="E68">
-        <v>-10.99452562334019</v>
+        <v>-9.469453317881017</v>
       </c>
       <c r="F68">
-        <v>-4.539543199574538</v>
+        <v>-4.148154038162411</v>
       </c>
       <c r="G68">
-        <v>-0.3575500005462399</v>
+        <v>-0.5007112318464831</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.284695724809446</v>
       </c>
       <c r="E69">
-        <v>-10.62728449521416</v>
+        <v>-8.199166545515398</v>
       </c>
       <c r="F69">
-        <v>-4.661310388147889</v>
+        <v>-4.328843005319686</v>
       </c>
       <c r="G69">
-        <v>0.02028256185078065</v>
+        <v>-1.797296323938661</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.542014773157344</v>
       </c>
       <c r="E70">
-        <v>-10.18055506283149</v>
+        <v>-8.11207946187389</v>
       </c>
       <c r="F70">
-        <v>-4.587467724281652</v>
+        <v>-4.38999464183255</v>
       </c>
       <c r="G70">
-        <v>-0.05622414556177648</v>
+        <v>-1.155881436250408</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.725281787142678</v>
       </c>
       <c r="E71">
-        <v>-11.31094368767815</v>
+        <v>-8.686167697248283</v>
       </c>
       <c r="F71">
-        <v>-4.639077532653992</v>
+        <v>-4.234759788001175</v>
       </c>
       <c r="G71">
-        <v>-0.9318866145177803</v>
+        <v>-1.407323991049133</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.831013497927093</v>
       </c>
       <c r="E72">
-        <v>-11.52144074497669</v>
+        <v>-9.749131872594738</v>
       </c>
       <c r="F72">
-        <v>-4.152352442544241</v>
+        <v>-4.495379184563636</v>
       </c>
       <c r="G72">
-        <v>-0.6929844062218145</v>
+        <v>-2.167243166861138</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.860057930632015</v>
       </c>
       <c r="E73">
-        <v>-11.17064703444651</v>
+        <v>-9.232052596502907</v>
       </c>
       <c r="F73">
-        <v>-4.296622508470071</v>
+        <v>-4.396793491327531</v>
       </c>
       <c r="G73">
-        <v>-0.7795584826192953</v>
+        <v>-0.9013832479189356</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.819149109691347</v>
       </c>
       <c r="E74">
-        <v>-11.585980556534</v>
+        <v>-10.37289746783328</v>
       </c>
       <c r="F74">
-        <v>-4.468546455238346</v>
+        <v>-4.637712378154884</v>
       </c>
       <c r="G74">
-        <v>-1.419622667727526</v>
+        <v>-1.106448370258011</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.717534776238457</v>
       </c>
       <c r="E75">
-        <v>-11.55697115204087</v>
+        <v>-10.68335153190313</v>
       </c>
       <c r="F75">
-        <v>-4.512564769305028</v>
+        <v>-4.597988282677916</v>
       </c>
       <c r="G75">
-        <v>-1.417752209497838</v>
+        <v>-1.694447605670123</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.569156710273031</v>
       </c>
       <c r="E76">
-        <v>-12.22507503628851</v>
+        <v>-9.98058217912677</v>
       </c>
       <c r="F76">
-        <v>-4.690083157219593</v>
+        <v>-4.647060202320765</v>
       </c>
       <c r="G76">
-        <v>-1.427395828653734</v>
+        <v>-0.9603672377921304</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.38652137502532</v>
       </c>
       <c r="E77">
-        <v>-11.95917662798013</v>
+        <v>-11.08537586888208</v>
       </c>
       <c r="F77">
-        <v>-4.524641318763211</v>
+        <v>-4.813471268797396</v>
       </c>
       <c r="G77">
-        <v>-1.457869400342726</v>
+        <v>-2.319796415856294</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.184557739387993</v>
       </c>
       <c r="E78">
-        <v>-12.8254374778554</v>
+        <v>-10.96377728482811</v>
       </c>
       <c r="F78">
-        <v>-4.518454571604547</v>
+        <v>-4.397396091428355</v>
       </c>
       <c r="G78">
-        <v>-0.8802785201060819</v>
+        <v>-1.771838228741666</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.973402547302666</v>
       </c>
       <c r="E79">
-        <v>-12.50575891223193</v>
+        <v>-11.40917987432654</v>
       </c>
       <c r="F79">
-        <v>-4.812471950364754</v>
+        <v>-4.283929897410781</v>
       </c>
       <c r="G79">
-        <v>-1.280837977630199</v>
+        <v>-1.277726064823284</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.763862510756213</v>
       </c>
       <c r="E80">
-        <v>-14.05652125073662</v>
+        <v>-11.58726211467818</v>
       </c>
       <c r="F80">
-        <v>-4.799290766030551</v>
+        <v>-4.537875557245581</v>
       </c>
       <c r="G80">
-        <v>-1.365286683791468</v>
+        <v>-1.53234674333971</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.561709923361907</v>
       </c>
       <c r="E81">
-        <v>-13.4884377718964</v>
+        <v>-12.58615743976411</v>
       </c>
       <c r="F81">
-        <v>-4.705665239721601</v>
+        <v>-4.67273524262187</v>
       </c>
       <c r="G81">
-        <v>-1.958135868418613</v>
+        <v>-1.876987776159997</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.371795785912573</v>
       </c>
       <c r="E82">
-        <v>-14.896272413771</v>
+        <v>-13.85388109584139</v>
       </c>
       <c r="F82">
-        <v>-4.858035961404904</v>
+        <v>-5.196940316926411</v>
       </c>
       <c r="G82">
-        <v>-1.065725349579436</v>
+        <v>-2.695503608017102</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.196542552836798</v>
       </c>
       <c r="E83">
-        <v>-14.02818206039662</v>
+        <v>-14.13476875311516</v>
       </c>
       <c r="F83">
-        <v>-4.746346685424452</v>
+        <v>-5.331636088740451</v>
       </c>
       <c r="G83">
-        <v>-1.847235903398567</v>
+        <v>-2.195866143593677</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.034705516609793</v>
       </c>
       <c r="E84">
-        <v>-16.15977100359912</v>
+        <v>-14.63331298509359</v>
       </c>
       <c r="F84">
-        <v>-4.874025848180138</v>
+        <v>-5.205721966227522</v>
       </c>
       <c r="G84">
-        <v>-1.917624722654551</v>
+        <v>-2.743546244883006</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.88740974825468</v>
       </c>
       <c r="E85">
-        <v>-16.9934449545152</v>
+        <v>-15.67651037139657</v>
       </c>
       <c r="F85">
-        <v>-5.000978881773595</v>
+        <v>-5.170935865794895</v>
       </c>
       <c r="G85">
-        <v>-1.970510687644409</v>
+        <v>-2.511486934216713</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.752262298272973</v>
       </c>
       <c r="E86">
-        <v>-18.36069541233306</v>
+        <v>-17.42903434083901</v>
       </c>
       <c r="F86">
-        <v>-5.007763477915338</v>
+        <v>-5.129990733057124</v>
       </c>
       <c r="G86">
-        <v>-1.189387467653372</v>
+        <v>-2.07088973894065</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.631296734726597</v>
       </c>
       <c r="E87">
-        <v>-20.54558902307985</v>
+        <v>-18.52770553373594</v>
       </c>
       <c r="F87">
-        <v>-5.000780126681208</v>
+        <v>-4.96509448128861</v>
       </c>
       <c r="G87">
-        <v>-2.214716389894287</v>
+        <v>-2.364478848999837</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.525036513724485</v>
       </c>
       <c r="E88">
-        <v>-20.55703700537124</v>
+        <v>-19.4850521098015</v>
       </c>
       <c r="F88">
-        <v>-4.940322153359307</v>
+        <v>-5.45282047353692</v>
       </c>
       <c r="G88">
-        <v>-2.424045494887943</v>
+        <v>-2.264765217356989</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.43523474049921</v>
       </c>
       <c r="E89">
-        <v>-23.17800002068664</v>
+        <v>-22.38950212647108</v>
       </c>
       <c r="F89">
-        <v>-5.014287554433991</v>
+        <v>-5.305212747394302</v>
       </c>
       <c r="G89">
-        <v>-2.850513281802397</v>
+        <v>-2.822165080349618</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.364044432117393</v>
       </c>
       <c r="E90">
-        <v>-23.62835676074945</v>
+        <v>-22.70820254170889</v>
       </c>
       <c r="F90">
-        <v>-4.930454873653161</v>
+        <v>-5.218707562881169</v>
       </c>
       <c r="G90">
-        <v>-2.840508813182719</v>
+        <v>-2.623058939981231</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.311059811634291</v>
       </c>
       <c r="E91">
-        <v>-25.56540698905645</v>
+        <v>-24.5489140139767</v>
       </c>
       <c r="F91">
-        <v>-5.093603505943987</v>
+        <v>-5.501945447327937</v>
       </c>
       <c r="G91">
-        <v>-2.898069268474027</v>
+        <v>-2.583117208049924</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.277564930458979</v>
       </c>
       <c r="E92">
-        <v>-26.98661421467569</v>
+        <v>-25.92423874095024</v>
       </c>
       <c r="F92">
-        <v>-5.282799349426045</v>
+        <v>-5.131016974490328</v>
       </c>
       <c r="G92">
-        <v>-3.198805846352501</v>
+        <v>-3.467380474316954</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.26180037019579</v>
       </c>
       <c r="E93">
-        <v>-29.24908964212189</v>
+        <v>-27.74079080438712</v>
       </c>
       <c r="F93">
-        <v>-5.428927102390685</v>
+        <v>-4.992797457014436</v>
       </c>
       <c r="G93">
-        <v>-3.175628717032063</v>
+        <v>-3.106583979265023</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.263043855085844</v>
       </c>
       <c r="E94">
-        <v>-31.5308835396848</v>
+        <v>-30.57319959230567</v>
       </c>
       <c r="F94">
-        <v>-5.255826462127239</v>
+        <v>-5.023815921074233</v>
       </c>
       <c r="G94">
-        <v>-4.010588028582728</v>
+        <v>-4.005258050264501</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.280394481482733</v>
       </c>
       <c r="E95">
-        <v>-33.38478192826295</v>
+        <v>-31.71102849994693</v>
       </c>
       <c r="F95">
-        <v>-5.239460445197087</v>
+        <v>-4.940311067417899</v>
       </c>
       <c r="G95">
-        <v>-3.722967832130847</v>
+        <v>-4.205645371756586</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.315878627000181</v>
       </c>
       <c r="E96">
-        <v>-35.77405462792392</v>
+        <v>-35.18388804558528</v>
       </c>
       <c r="F96">
-        <v>-4.984277911042329</v>
+        <v>-5.309754024106825</v>
       </c>
       <c r="G96">
-        <v>-3.928804311580572</v>
+        <v>-4.229070791992469</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.368676408146539</v>
       </c>
       <c r="E97">
-        <v>-37.626734856994</v>
+        <v>-37.49300222683648</v>
       </c>
       <c r="F97">
-        <v>-5.111180266046492</v>
+        <v>-4.798260565332558</v>
       </c>
       <c r="G97">
-        <v>-4.055452541730931</v>
+        <v>-5.073011613591176</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.4498510136618</v>
       </c>
       <c r="E98">
-        <v>-40.73492091926866</v>
+        <v>-38.28261865413194</v>
       </c>
       <c r="F98">
-        <v>-4.923599802598182</v>
+        <v>-5.112985690790093</v>
       </c>
       <c r="G98">
-        <v>-5.160790728564952</v>
+        <v>-5.308590034165714</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.554804969135005</v>
       </c>
       <c r="E99">
-        <v>-43.95923743323303</v>
+        <v>-42.97974888350696</v>
       </c>
       <c r="F99">
-        <v>-4.993437274204273</v>
+        <v>-5.086012803491286</v>
       </c>
       <c r="G99">
-        <v>-5.374006414021713</v>
+        <v>-5.497198434629072</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.709824126618618</v>
       </c>
       <c r="E100">
-        <v>-45.31200583117435</v>
+        <v>-44.06485956098793</v>
       </c>
       <c r="F100">
-        <v>-5.133422623775881</v>
+        <v>-4.677529120427905</v>
       </c>
       <c r="G100">
-        <v>-5.178452489016964</v>
+        <v>-6.074822420321109</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.89385339129355</v>
       </c>
       <c r="E101">
-        <v>-47.83409640924329</v>
+        <v>-45.99287774788662</v>
       </c>
       <c r="F101">
-        <v>-5.100115704668274</v>
+        <v>-4.626961390547923</v>
       </c>
       <c r="G101">
-        <v>-5.714164968181827</v>
+        <v>-6.185762111887626</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.16799909398839</v>
       </c>
       <c r="E102">
-        <v>-49.61400292889161</v>
+        <v>-49.03155399838055</v>
       </c>
       <c r="F102">
-        <v>-4.63467878947386</v>
+        <v>-4.303472828407304</v>
       </c>
       <c r="G102">
-        <v>-6.214001065337609</v>
+        <v>-6.721928135791369</v>
       </c>
     </row>
   </sheetData>
